--- a/data_scraping/flight/flight_tiket.xlsx
+++ b/data_scraping/flight/flight_tiket.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\manpro-project\data-scraping\flight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\manpro-project\data_scraping\flight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EE4290-0C2C-4AE2-B419-1B42814190F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0721341-CB17-4791-81EF-CEC0C62EC5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8665" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8665" uniqueCount="512">
   <si>
     <t>date</t>
   </si>
@@ -1471,9 +1471,6 @@
   </si>
   <si>
     <t>795744</t>
-  </si>
-  <si>
-    <t>JKT</t>
   </si>
   <si>
     <t>10:50</t>
@@ -32307,7 +32304,7 @@
         <v>252</v>
       </c>
       <c r="I871" s="1" t="s">
-        <v>482</v>
+        <v>17</v>
       </c>
       <c r="J871" s="1" t="s">
         <v>19</v>
@@ -32324,7 +32321,7 @@
         <v>254</v>
       </c>
       <c r="C872" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D872" s="1" t="s">
         <v>255</v>
@@ -32336,7 +32333,7 @@
         <v>0</v>
       </c>
       <c r="G872" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H872" s="1" t="s">
         <v>17</v>
@@ -32371,7 +32368,7 @@
         <v>0</v>
       </c>
       <c r="G873" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H873" s="1" t="s">
         <v>17</v>
@@ -32397,7 +32394,7 @@
         <v>289</v>
       </c>
       <c r="D874" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E874" s="1" t="s">
         <v>463</v>
@@ -32406,7 +32403,7 @@
         <v>0</v>
       </c>
       <c r="G874" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H874" s="1" t="s">
         <v>17</v>
@@ -32429,7 +32426,7 @@
         <v>254</v>
       </c>
       <c r="C875" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D875" s="1" t="s">
         <v>249</v>
@@ -32441,7 +32438,7 @@
         <v>0</v>
       </c>
       <c r="G875" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H875" s="1" t="s">
         <v>17</v>
@@ -32476,7 +32473,7 @@
         <v>0</v>
       </c>
       <c r="G876" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H876" s="1" t="s">
         <v>17</v>
@@ -32499,7 +32496,7 @@
         <v>254</v>
       </c>
       <c r="C877" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D877" s="1" t="s">
         <v>249</v>
@@ -32511,7 +32508,7 @@
         <v>0</v>
       </c>
       <c r="G877" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H877" s="1" t="s">
         <v>17</v>
@@ -32546,7 +32543,7 @@
         <v>0</v>
       </c>
       <c r="G878" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H878" s="1" t="s">
         <v>17</v>
@@ -32569,7 +32566,7 @@
         <v>254</v>
       </c>
       <c r="C879" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D879" s="1" t="s">
         <v>255</v>
@@ -32581,7 +32578,7 @@
         <v>0</v>
       </c>
       <c r="G879" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H879" s="1" t="s">
         <v>17</v>
@@ -32604,7 +32601,7 @@
         <v>254</v>
       </c>
       <c r="C880" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D880" s="1" t="s">
         <v>249</v>
@@ -32616,7 +32613,7 @@
         <v>0</v>
       </c>
       <c r="G880" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H880" s="1" t="s">
         <v>17</v>
@@ -32651,7 +32648,7 @@
         <v>0</v>
       </c>
       <c r="G881" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H881" s="1" t="s">
         <v>17</v>
@@ -32674,7 +32671,7 @@
         <v>254</v>
       </c>
       <c r="C882" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D882" s="1" t="s">
         <v>213</v>
@@ -32686,7 +32683,7 @@
         <v>0</v>
       </c>
       <c r="G882" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H882" s="1" t="s">
         <v>17</v>
@@ -32709,7 +32706,7 @@
         <v>20</v>
       </c>
       <c r="C883" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D883" s="1" t="s">
         <v>249</v>
@@ -32721,7 +32718,7 @@
         <v>0</v>
       </c>
       <c r="G883" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H883" s="1" t="s">
         <v>17</v>
@@ -32756,7 +32753,7 @@
         <v>0</v>
       </c>
       <c r="G884" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H884" s="1" t="s">
         <v>17</v>
@@ -32791,7 +32788,7 @@
         <v>0</v>
       </c>
       <c r="G885" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H885" s="1" t="s">
         <v>17</v>
@@ -32826,7 +32823,7 @@
         <v>0</v>
       </c>
       <c r="G886" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H886" s="1" t="s">
         <v>17</v>
@@ -32849,7 +32846,7 @@
         <v>254</v>
       </c>
       <c r="C887" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D887" s="1" t="s">
         <v>249</v>
@@ -32861,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="G887" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H887" s="1" t="s">
         <v>17</v>
@@ -32896,7 +32893,7 @@
         <v>0</v>
       </c>
       <c r="G888" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H888" s="1" t="s">
         <v>17</v>
@@ -32919,7 +32916,7 @@
         <v>12</v>
       </c>
       <c r="C889" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D889" s="1" t="s">
         <v>249</v>
@@ -32931,7 +32928,7 @@
         <v>0</v>
       </c>
       <c r="G889" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H889" s="1" t="s">
         <v>17</v>
@@ -32954,7 +32951,7 @@
         <v>254</v>
       </c>
       <c r="C890" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D890" s="1" t="s">
         <v>294</v>
@@ -32966,7 +32963,7 @@
         <v>0</v>
       </c>
       <c r="G890" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H890" s="1" t="s">
         <v>17</v>
@@ -33001,7 +32998,7 @@
         <v>0</v>
       </c>
       <c r="G891" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H891" s="1" t="s">
         <v>17</v>
@@ -33027,7 +33024,7 @@
         <v>206</v>
       </c>
       <c r="D892" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E892" s="1" t="s">
         <v>469</v>
@@ -33036,7 +33033,7 @@
         <v>0</v>
       </c>
       <c r="G892" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H892" s="1" t="s">
         <v>17</v>
@@ -33059,7 +33056,7 @@
         <v>254</v>
       </c>
       <c r="C893" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D893" s="1" t="s">
         <v>249</v>
@@ -33071,7 +33068,7 @@
         <v>0</v>
       </c>
       <c r="G893" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H893" s="1" t="s">
         <v>17</v>
@@ -33094,7 +33091,7 @@
         <v>254</v>
       </c>
       <c r="C894" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D894" s="1" t="s">
         <v>255</v>
@@ -33106,7 +33103,7 @@
         <v>0</v>
       </c>
       <c r="G894" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H894" s="1" t="s">
         <v>17</v>
@@ -33129,7 +33126,7 @@
         <v>254</v>
       </c>
       <c r="C895" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D895" s="1" t="s">
         <v>249</v>
@@ -33141,7 +33138,7 @@
         <v>0</v>
       </c>
       <c r="G895" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H895" s="1" t="s">
         <v>17</v>
@@ -33176,7 +33173,7 @@
         <v>0</v>
       </c>
       <c r="G896" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H896" s="1" t="s">
         <v>17</v>
@@ -33211,7 +33208,7 @@
         <v>0</v>
       </c>
       <c r="G897" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H897" s="1" t="s">
         <v>17</v>
@@ -33234,7 +33231,7 @@
         <v>254</v>
       </c>
       <c r="C898" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D898" s="1" t="s">
         <v>249</v>
@@ -33246,7 +33243,7 @@
         <v>0</v>
       </c>
       <c r="G898" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H898" s="1" t="s">
         <v>17</v>
@@ -33281,7 +33278,7 @@
         <v>0</v>
       </c>
       <c r="G899" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H899" s="1" t="s">
         <v>17</v>
@@ -33304,7 +33301,7 @@
         <v>254</v>
       </c>
       <c r="C900" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D900" s="1" t="s">
         <v>294</v>
@@ -33316,7 +33313,7 @@
         <v>0</v>
       </c>
       <c r="G900" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H900" s="1" t="s">
         <v>17</v>
@@ -33339,7 +33336,7 @@
         <v>254</v>
       </c>
       <c r="C901" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D901" s="1" t="s">
         <v>249</v>
@@ -33351,7 +33348,7 @@
         <v>0</v>
       </c>
       <c r="G901" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H901" s="1" t="s">
         <v>17</v>
@@ -33386,7 +33383,7 @@
         <v>0</v>
       </c>
       <c r="G902" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H902" s="1" t="s">
         <v>17</v>
@@ -33409,7 +33406,7 @@
         <v>20</v>
       </c>
       <c r="C903" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D903" s="1" t="s">
         <v>289</v>
@@ -33421,7 +33418,7 @@
         <v>0</v>
       </c>
       <c r="G903" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H903" s="1" t="s">
         <v>17</v>
@@ -33444,19 +33441,19 @@
         <v>20</v>
       </c>
       <c r="C904" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D904" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E904" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F904" s="1">
+        <v>0</v>
+      </c>
+      <c r="G904" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F904" s="1">
-        <v>0</v>
-      </c>
-      <c r="G904" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H904" s="1" t="s">
         <v>252</v>
@@ -33485,13 +33482,13 @@
         <v>193</v>
       </c>
       <c r="E905" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F905" s="1">
+        <v>0</v>
+      </c>
+      <c r="G905" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F905" s="1">
-        <v>0</v>
-      </c>
-      <c r="G905" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H905" s="1" t="s">
         <v>252</v>
@@ -33520,13 +33517,13 @@
         <v>14</v>
       </c>
       <c r="E906" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F906" s="1">
+        <v>0</v>
+      </c>
+      <c r="G906" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F906" s="1">
-        <v>0</v>
-      </c>
-      <c r="G906" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H906" s="1" t="s">
         <v>252</v>
@@ -33555,13 +33552,13 @@
         <v>97</v>
       </c>
       <c r="E907" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F907" s="1">
+        <v>0</v>
+      </c>
+      <c r="G907" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F907" s="1">
-        <v>0</v>
-      </c>
-      <c r="G907" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H907" s="1" t="s">
         <v>252</v>
@@ -33590,13 +33587,13 @@
         <v>241</v>
       </c>
       <c r="E908" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F908" s="1">
+        <v>0</v>
+      </c>
+      <c r="G908" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F908" s="1">
-        <v>0</v>
-      </c>
-      <c r="G908" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H908" s="1" t="s">
         <v>252</v>
@@ -33619,19 +33616,19 @@
         <v>20</v>
       </c>
       <c r="C909" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D909" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E909" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F909" s="1">
+        <v>0</v>
+      </c>
+      <c r="G909" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F909" s="1">
-        <v>0</v>
-      </c>
-      <c r="G909" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H909" s="1" t="s">
         <v>252</v>
@@ -33660,13 +33657,13 @@
         <v>97</v>
       </c>
       <c r="E910" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F910" s="1">
+        <v>0</v>
+      </c>
+      <c r="G910" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F910" s="1">
-        <v>0</v>
-      </c>
-      <c r="G910" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H910" s="1" t="s">
         <v>252</v>
@@ -33695,13 +33692,13 @@
         <v>241</v>
       </c>
       <c r="E911" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F911" s="1">
+        <v>0</v>
+      </c>
+      <c r="G911" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F911" s="1">
-        <v>0</v>
-      </c>
-      <c r="G911" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H911" s="1" t="s">
         <v>252</v>
@@ -33724,19 +33721,19 @@
         <v>20</v>
       </c>
       <c r="C912" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D912" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E912" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F912" s="1">
+        <v>0</v>
+      </c>
+      <c r="G912" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F912" s="1">
-        <v>0</v>
-      </c>
-      <c r="G912" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H912" s="1" t="s">
         <v>252</v>
@@ -33765,13 +33762,13 @@
         <v>97</v>
       </c>
       <c r="E913" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F913" s="1">
+        <v>0</v>
+      </c>
+      <c r="G913" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F913" s="1">
-        <v>0</v>
-      </c>
-      <c r="G913" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H913" s="1" t="s">
         <v>252</v>
@@ -33794,19 +33791,19 @@
         <v>20</v>
       </c>
       <c r="C914" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D914" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E914" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F914" s="1">
+        <v>0</v>
+      </c>
+      <c r="G914" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F914" s="1">
-        <v>0</v>
-      </c>
-      <c r="G914" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H914" s="1" t="s">
         <v>252</v>
@@ -33835,13 +33832,13 @@
         <v>193</v>
       </c>
       <c r="E915" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F915" s="1">
+        <v>0</v>
+      </c>
+      <c r="G915" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F915" s="1">
-        <v>0</v>
-      </c>
-      <c r="G915" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H915" s="1" t="s">
         <v>252</v>
@@ -33876,7 +33873,7 @@
         <v>0</v>
       </c>
       <c r="G916" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H916" s="1" t="s">
         <v>252</v>
@@ -33911,7 +33908,7 @@
         <v>0</v>
       </c>
       <c r="G917" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H917" s="1" t="s">
         <v>252</v>
@@ -33937,7 +33934,7 @@
         <v>387</v>
       </c>
       <c r="D918" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E918" s="1" t="s">
         <v>463</v>
@@ -33946,7 +33943,7 @@
         <v>0</v>
       </c>
       <c r="G918" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H918" s="1" t="s">
         <v>252</v>
@@ -33969,19 +33966,19 @@
         <v>20</v>
       </c>
       <c r="C919" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D919" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E919" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F919" s="1">
+        <v>0</v>
+      </c>
+      <c r="G919" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F919" s="1">
-        <v>0</v>
-      </c>
-      <c r="G919" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H919" s="1" t="s">
         <v>252</v>
@@ -34010,13 +34007,13 @@
         <v>193</v>
       </c>
       <c r="E920" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F920" s="1">
+        <v>0</v>
+      </c>
+      <c r="G920" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F920" s="1">
-        <v>0</v>
-      </c>
-      <c r="G920" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H920" s="1" t="s">
         <v>252</v>
@@ -34039,19 +34036,19 @@
         <v>20</v>
       </c>
       <c r="C921" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D921" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D921" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="E921" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F921" s="1">
+        <v>0</v>
+      </c>
+      <c r="G921" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F921" s="1">
-        <v>0</v>
-      </c>
-      <c r="G921" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H921" s="1" t="s">
         <v>252</v>
@@ -34080,13 +34077,13 @@
         <v>97</v>
       </c>
       <c r="E922" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F922" s="1">
+        <v>0</v>
+      </c>
+      <c r="G922" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F922" s="1">
-        <v>0</v>
-      </c>
-      <c r="G922" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H922" s="1" t="s">
         <v>252</v>
@@ -34121,7 +34118,7 @@
         <v>0</v>
       </c>
       <c r="G923" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H923" s="1" t="s">
         <v>252</v>
@@ -34147,7 +34144,7 @@
         <v>387</v>
       </c>
       <c r="D924" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E924" s="1" t="s">
         <v>463</v>
@@ -34156,7 +34153,7 @@
         <v>0</v>
       </c>
       <c r="G924" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H924" s="1" t="s">
         <v>252</v>
@@ -34185,13 +34182,13 @@
         <v>193</v>
       </c>
       <c r="E925" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F925" s="1">
+        <v>0</v>
+      </c>
+      <c r="G925" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F925" s="1">
-        <v>0</v>
-      </c>
-      <c r="G925" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H925" s="1" t="s">
         <v>252</v>
@@ -34226,7 +34223,7 @@
         <v>0</v>
       </c>
       <c r="G926" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H926" s="1" t="s">
         <v>252</v>
@@ -34261,7 +34258,7 @@
         <v>0</v>
       </c>
       <c r="G927" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H927" s="1" t="s">
         <v>252</v>
@@ -34290,13 +34287,13 @@
         <v>241</v>
       </c>
       <c r="E928" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F928" s="1">
+        <v>0</v>
+      </c>
+      <c r="G928" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F928" s="1">
-        <v>0</v>
-      </c>
-      <c r="G928" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H928" s="1" t="s">
         <v>252</v>
@@ -34319,19 +34316,19 @@
         <v>20</v>
       </c>
       <c r="C929" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D929" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E929" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F929" s="1">
+        <v>0</v>
+      </c>
+      <c r="G929" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F929" s="1">
-        <v>0</v>
-      </c>
-      <c r="G929" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H929" s="1" t="s">
         <v>252</v>
@@ -34360,13 +34357,13 @@
         <v>97</v>
       </c>
       <c r="E930" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F930" s="1">
+        <v>0</v>
+      </c>
+      <c r="G930" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F930" s="1">
-        <v>0</v>
-      </c>
-      <c r="G930" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H930" s="1" t="s">
         <v>252</v>
@@ -34389,19 +34386,19 @@
         <v>20</v>
       </c>
       <c r="C931" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D931" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E931" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F931" s="1">
+        <v>0</v>
+      </c>
+      <c r="G931" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F931" s="1">
-        <v>0</v>
-      </c>
-      <c r="G931" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H931" s="1" t="s">
         <v>252</v>
@@ -34424,19 +34421,19 @@
         <v>20</v>
       </c>
       <c r="C932" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D932" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E932" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F932" s="1">
+        <v>0</v>
+      </c>
+      <c r="G932" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F932" s="1">
-        <v>0</v>
-      </c>
-      <c r="G932" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H932" s="1" t="s">
         <v>252</v>
@@ -34465,13 +34462,13 @@
         <v>193</v>
       </c>
       <c r="E933" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F933" s="1">
+        <v>0</v>
+      </c>
+      <c r="G933" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F933" s="1">
-        <v>0</v>
-      </c>
-      <c r="G933" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H933" s="1" t="s">
         <v>252</v>
@@ -34494,19 +34491,19 @@
         <v>20</v>
       </c>
       <c r="C934" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D934" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D934" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="E934" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F934" s="1">
+        <v>0</v>
+      </c>
+      <c r="G934" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F934" s="1">
-        <v>0</v>
-      </c>
-      <c r="G934" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H934" s="1" t="s">
         <v>252</v>
@@ -34535,13 +34532,13 @@
         <v>14</v>
       </c>
       <c r="E935" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F935" s="1">
+        <v>0</v>
+      </c>
+      <c r="G935" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F935" s="1">
-        <v>0</v>
-      </c>
-      <c r="G935" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H935" s="1" t="s">
         <v>252</v>
@@ -34570,13 +34567,13 @@
         <v>402</v>
       </c>
       <c r="E936" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F936" s="1">
+        <v>0</v>
+      </c>
+      <c r="G936" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F936" s="1">
-        <v>0</v>
-      </c>
-      <c r="G936" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H936" s="1" t="s">
         <v>17</v>
@@ -34599,19 +34596,19 @@
         <v>20</v>
       </c>
       <c r="C937" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D937" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="D937" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="E937" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F937" s="1">
+        <v>0</v>
+      </c>
+      <c r="G937" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F937" s="1">
-        <v>0</v>
-      </c>
-      <c r="G937" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H937" s="1" t="s">
         <v>17</v>
@@ -34634,19 +34631,19 @@
         <v>20</v>
       </c>
       <c r="C938" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D938" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D938" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="E938" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F938" s="1">
+        <v>0</v>
+      </c>
+      <c r="G938" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F938" s="1">
-        <v>0</v>
-      </c>
-      <c r="G938" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H938" s="1" t="s">
         <v>17</v>
@@ -34681,7 +34678,7 @@
         <v>0</v>
       </c>
       <c r="G939" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H939" s="1" t="s">
         <v>17</v>
@@ -34710,13 +34707,13 @@
         <v>461</v>
       </c>
       <c r="E940" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F940" s="1">
+        <v>0</v>
+      </c>
+      <c r="G940" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F940" s="1">
-        <v>0</v>
-      </c>
-      <c r="G940" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H940" s="1" t="s">
         <v>17</v>
@@ -34742,16 +34739,16 @@
         <v>243</v>
       </c>
       <c r="D941" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E941" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F941" s="1">
+        <v>0</v>
+      </c>
+      <c r="G941" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F941" s="1">
-        <v>0</v>
-      </c>
-      <c r="G941" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H941" s="1" t="s">
         <v>17</v>
@@ -34774,19 +34771,19 @@
         <v>20</v>
       </c>
       <c r="C942" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D942" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E942" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F942" s="1">
+        <v>0</v>
+      </c>
+      <c r="G942" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F942" s="1">
-        <v>0</v>
-      </c>
-      <c r="G942" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H942" s="1" t="s">
         <v>17</v>
@@ -34815,13 +34812,13 @@
         <v>461</v>
       </c>
       <c r="E943" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F943" s="1">
+        <v>0</v>
+      </c>
+      <c r="G943" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F943" s="1">
-        <v>0</v>
-      </c>
-      <c r="G943" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H943" s="1" t="s">
         <v>17</v>
@@ -34847,16 +34844,16 @@
         <v>243</v>
       </c>
       <c r="D944" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E944" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F944" s="1">
+        <v>0</v>
+      </c>
+      <c r="G944" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F944" s="1">
-        <v>0</v>
-      </c>
-      <c r="G944" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H944" s="1" t="s">
         <v>17</v>
@@ -34879,19 +34876,19 @@
         <v>20</v>
       </c>
       <c r="C945" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D945" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E945" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F945" s="1">
+        <v>0</v>
+      </c>
+      <c r="G945" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F945" s="1">
-        <v>0</v>
-      </c>
-      <c r="G945" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H945" s="1" t="s">
         <v>17</v>
@@ -34917,16 +34914,16 @@
         <v>243</v>
       </c>
       <c r="D946" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E946" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F946" s="1">
+        <v>0</v>
+      </c>
+      <c r="G946" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F946" s="1">
-        <v>0</v>
-      </c>
-      <c r="G946" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H946" s="1" t="s">
         <v>17</v>
@@ -34955,13 +34952,13 @@
         <v>402</v>
       </c>
       <c r="E947" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F947" s="1">
+        <v>0</v>
+      </c>
+      <c r="G947" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F947" s="1">
-        <v>0</v>
-      </c>
-      <c r="G947" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H947" s="1" t="s">
         <v>17</v>
@@ -34984,10 +34981,10 @@
         <v>20</v>
       </c>
       <c r="C948" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D948" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="D948" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="E948" s="1" t="s">
         <v>469</v>
@@ -34996,7 +34993,7 @@
         <v>0</v>
       </c>
       <c r="G948" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H948" s="1" t="s">
         <v>17</v>
@@ -35031,7 +35028,7 @@
         <v>0</v>
       </c>
       <c r="G949" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H949" s="1" t="s">
         <v>17</v>
@@ -35054,19 +35051,19 @@
         <v>20</v>
       </c>
       <c r="C950" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D950" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E950" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F950" s="1">
+        <v>0</v>
+      </c>
+      <c r="G950" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F950" s="1">
-        <v>0</v>
-      </c>
-      <c r="G950" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H950" s="1" t="s">
         <v>17</v>
@@ -35092,16 +35089,16 @@
         <v>243</v>
       </c>
       <c r="D951" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E951" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F951" s="1">
+        <v>0</v>
+      </c>
+      <c r="G951" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F951" s="1">
-        <v>0</v>
-      </c>
-      <c r="G951" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H951" s="1" t="s">
         <v>17</v>
@@ -35130,13 +35127,13 @@
         <v>402</v>
       </c>
       <c r="E952" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F952" s="1">
+        <v>0</v>
+      </c>
+      <c r="G952" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F952" s="1">
-        <v>0</v>
-      </c>
-      <c r="G952" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H952" s="1" t="s">
         <v>17</v>
@@ -35159,19 +35156,19 @@
         <v>20</v>
       </c>
       <c r="C953" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D953" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E953" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F953" s="1">
+        <v>0</v>
+      </c>
+      <c r="G953" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F953" s="1">
-        <v>0</v>
-      </c>
-      <c r="G953" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H953" s="1" t="s">
         <v>17</v>
@@ -35200,13 +35197,13 @@
         <v>461</v>
       </c>
       <c r="E954" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F954" s="1">
+        <v>0</v>
+      </c>
+      <c r="G954" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F954" s="1">
-        <v>0</v>
-      </c>
-      <c r="G954" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H954" s="1" t="s">
         <v>17</v>
@@ -35232,16 +35229,16 @@
         <v>243</v>
       </c>
       <c r="D955" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E955" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F955" s="1">
+        <v>0</v>
+      </c>
+      <c r="G955" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F955" s="1">
-        <v>0</v>
-      </c>
-      <c r="G955" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H955" s="1" t="s">
         <v>17</v>
@@ -35270,13 +35267,13 @@
         <v>402</v>
       </c>
       <c r="E956" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F956" s="1">
+        <v>0</v>
+      </c>
+      <c r="G956" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F956" s="1">
-        <v>0</v>
-      </c>
-      <c r="G956" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H956" s="1" t="s">
         <v>17</v>
@@ -35299,19 +35296,19 @@
         <v>20</v>
       </c>
       <c r="C957" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D957" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="D957" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="E957" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F957" s="1">
+        <v>0</v>
+      </c>
+      <c r="G957" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F957" s="1">
-        <v>0</v>
-      </c>
-      <c r="G957" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H957" s="1" t="s">
         <v>17</v>
@@ -35334,19 +35331,19 @@
         <v>20</v>
       </c>
       <c r="C958" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D958" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D958" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="E958" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F958" s="1">
+        <v>0</v>
+      </c>
+      <c r="G958" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F958" s="1">
-        <v>0</v>
-      </c>
-      <c r="G958" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H958" s="1" t="s">
         <v>17</v>
@@ -35369,19 +35366,19 @@
         <v>20</v>
       </c>
       <c r="C959" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D959" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E959" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F959" s="1">
+        <v>0</v>
+      </c>
+      <c r="G959" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F959" s="1">
-        <v>0</v>
-      </c>
-      <c r="G959" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H959" s="1" t="s">
         <v>17</v>
@@ -35407,16 +35404,16 @@
         <v>243</v>
       </c>
       <c r="D960" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E960" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F960" s="1">
+        <v>0</v>
+      </c>
+      <c r="G960" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F960" s="1">
-        <v>0</v>
-      </c>
-      <c r="G960" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H960" s="1" t="s">
         <v>17</v>
@@ -35445,13 +35442,13 @@
         <v>402</v>
       </c>
       <c r="E961" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F961" s="1">
+        <v>0</v>
+      </c>
+      <c r="G961" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F961" s="1">
-        <v>0</v>
-      </c>
-      <c r="G961" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H961" s="1" t="s">
         <v>17</v>
@@ -35474,19 +35471,19 @@
         <v>20</v>
       </c>
       <c r="C962" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D962" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E962" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F962" s="1">
+        <v>0</v>
+      </c>
+      <c r="G962" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F962" s="1">
-        <v>0</v>
-      </c>
-      <c r="G962" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H962" s="1" t="s">
         <v>17</v>
@@ -35512,16 +35509,16 @@
         <v>243</v>
       </c>
       <c r="D963" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E963" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F963" s="1">
+        <v>0</v>
+      </c>
+      <c r="G963" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F963" s="1">
-        <v>0</v>
-      </c>
-      <c r="G963" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H963" s="1" t="s">
         <v>17</v>
@@ -35550,13 +35547,13 @@
         <v>402</v>
       </c>
       <c r="E964" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F964" s="1">
+        <v>0</v>
+      </c>
+      <c r="G964" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F964" s="1">
-        <v>0</v>
-      </c>
-      <c r="G964" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H964" s="1" t="s">
         <v>17</v>
@@ -35585,13 +35582,13 @@
         <v>402</v>
       </c>
       <c r="E965" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F965" s="1">
+        <v>0</v>
+      </c>
+      <c r="G965" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F965" s="1">
-        <v>0</v>
-      </c>
-      <c r="G965" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H965" s="1" t="s">
         <v>17</v>
@@ -35617,16 +35614,16 @@
         <v>346</v>
       </c>
       <c r="D966" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E966" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F966" s="1">
+        <v>0</v>
+      </c>
+      <c r="G966" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F966" s="1">
-        <v>0</v>
-      </c>
-      <c r="G966" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H966" s="1" t="s">
         <v>17</v>
